--- a/Contact_Log_Consulting_Partner_DACH.xlsx
+++ b/Contact_Log_Consulting_Partner_DACH.xlsx
@@ -48,7 +48,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,7 +62,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,23 +102,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,16 +486,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
@@ -535,7 +547,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Alvarez &amp; Marsal</t>
@@ -543,24 +555,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Jürgen Zapf</t>
+          <t>Johann Stohner</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Co-Head A&amp;M Deutschland (zugl. Head of German Transaction Advisory Group)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>jzapf@alvarezandmarsal.com</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: [Initial Vorname][Nachname]@alvarezandmarsal.com; Beleg jstohner@alvarezandmarsal.com)</t>
+          <t>Managing Director, Head of Restructuring Germany</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 71040 600</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>+49 170 921 3836</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>jstohner@alvarezandmarsal.com</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>BESTÄTIGT - https://www.germany-alvarezandmarsal.com/en/contact-us (Adresse dort mit Telefonnummer veröffentlicht)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -570,50 +590,54 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal Deutschland GmbH, Neue Mainzer Str. 28, 60311 Frankfurt am Main</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>Alvarez &amp; Marsal Deutschland GmbH, Sonnenstraße 20, 80331 München</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FTI Andersch</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Christian Säuberlich</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Sprecher des Vorstands, Senior Partner</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Sprecher des Vorstands, Senior Partner; zugleich Country Leader DACH bei FTI Consulting</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>+49 69 2722995-0</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>christian.saeuberlich@fti-andersch.com</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: vorname.nachname@fti-andersch.com; Umlaut-Schreibweise unbestätigt – Rückfall: info@fti-andersch.com)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Firmenschema (zwei Belege: leoni.juschkat@ und ellina.hanxleden@fti-andersch.com; Umlaut-Schreibweise gestützt durch Seiten-URL .../management/christian-saeuberlich/) - Rückfall: info@fti-andersch.com</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Herr</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>FTI-Andersch AG, Taunusanlage 9-10, 60329 Frankfurt am Main</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="50" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FRP</t>
@@ -629,16 +653,20 @@
           <t>Group Chief Executive Officer &amp; Co-Founder</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>+44 20 3005 4289</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>geoff.rowley@frpadvisory.com</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frpadvisory.com/about-us/our-people/geoff-rowley/</t>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>BESTÄTIGT - https://www.frpadvisory.com/about-us/our-people/geoff-rowley/</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -652,46 +680,50 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Investec</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Jürgen Schwarz</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Managing Partner Germany; Leiter Restructuring Deutschland (Capitalmind Investec)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>+49 611 205 48 10</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>contact-de@capitalmind.com</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>https://capitalmind.com/contact/ (allgemeiner offizieller Kontakt; persönliches Postfach nicht veröffentlicht)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - https://capitalmind.com/contact/ (persönliches Postfach nicht veröffentlicht; Domainwechsel Richtung investec.com laufend)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Herr</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Investec Advisory GmbH &amp; Co. KG, Sonnenberger Straße 16, 65193 Wiesbaden</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Piper Sandler</t>
@@ -709,14 +741,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>christian.hess@psc.com</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: vorname.nachname@psc.com; Belege matt.morrell@psc.com, michael.bailey@psc.com)</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>SCHWACH BELEGT - Maildomain psc.com offiziell (investorrelations@psc.com), Personenschema vorname.nachname aber nur über maskierte Datenbank-Treffer. Vor Versand verifizieren.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -730,46 +762,50 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Stifel</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Christian Stippler</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Managing Director, Investment Banking Frankfurt; Geschäftsführer Stifel Europe Advisory GmbH</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Business Services / Diversified Industries Investment Banking, Frankfurt</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>+49 69 247414 119</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>stipplerc@stifel.com</t>
+          <t>christian.stippler@stifel.com</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Firmenschema (abgeleitet: [Nachname][Initial Vorname]@stifel.com; Beleg shapiron@stifel.com)</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+          <t>BESTÄTIGT - https://stifelinstitutional.com/meet/christian-stippler/ (Adresse, Telefon und v-Card auf der Profilseite)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Herr</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Stifel Europe Advisory GmbH, Luginsland 1, 60313 Frankfurt am Main</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Forvis Mazars</t>
@@ -785,16 +821,20 @@
           <t>CEO / Sprecher des Vorstands, Forvis Mazars in Deutschland</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>+49 30 208 88-1210</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>contact-de@forvismazars.com</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.forvismazars.com/de/de/legals/impressum (allgemeiner offizieller Kontakt; persönliches Postfach nicht veröffentlicht)</t>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - https://www.forvismazars.com/de/de/legals/impressum (persönliches Postfach nicht veröffentlicht; Altdomain mazars.de parallel aktiv)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -808,46 +848,50 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Oliver Wyman</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Fabian Brandt</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Market Leader Deutschland &amp; Österreich; Geschäftsführer Oliver Wyman GmbH</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 939 49 0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>fabian.brandt@oliverwyman.com</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: vorname.nachname@oliverwyman.com; Beleg felix.wilker@oliverwyman.com)</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Firmenschema (drei Belege auf oliverwyman.de: felix.wilker@, davina.lermer-spitzweg@, aleksandar.nikolov@oliverwyman.com)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Herr</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Oliver Wyman GmbH, Müllerstraße 3, 80469 München</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Roland Berger</t>
@@ -863,16 +907,20 @@
           <t>Global Managing Partner, Sprecher der Geschäftsführung (verantwortet Deutschland/Zentraleuropa)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 9230 0</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>stefan.schaible@rolandberger.com</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: vorname.nachname@rolandberger.com; Belege silvia.zoesch@ / julia.frank@rolandberger.com)</t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Firmenschema (drei Belege im offiziellen Newsroom: silvia.zoesch@, julia.frank@, philipp.topitsch@rolandberger.com)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -886,98 +934,122 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Ankura</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Jens Nawrath</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Senior Managing Director, Leiter Turnaround &amp; Restructuring Deutschland</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>jens.nawrath@ankura.com</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Firmenschema (abgeleitet: vorname.nachname@ankura.com; Beleg robin.boesen@ankura.com)</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Firmenschema, nur EIN Beleg (robin.boesen@ankura.com aus der offiziellen Pressemitteilung vom 14.08.2025) - vor Versand verifizieren</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Herr</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Ankura Consulting Group, Taunusanlage 21, 60325 Frankfurt am Main</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Hinweise zur Spalte "Herkunft Email"</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Legende Spalte "Herkunft Email" (Farbe in Spalte Email/Herkunft)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>URL = Adresse ist auf der genannten offiziellen Unternehmensseite veröffentlicht (bestätigt).</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>GRUEN  "BESTAETIGT" + URL = Adresse steht so auf der genannten offiziellen Unternehmensseite. Direkt verwendbar.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>"Firmenschema (abgeleitet)" = Adresse aus dem belegten E-Mail-Muster desselben Unternehmens gebildet; Mailbox nicht verifiziert.</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>GELB   "Firmenschema" = aus dem belegten Muster desselben Unternehmens gebildet, Mailbox nicht verifiziert. Anzahl der Belege ist jeweils genannt.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Es wurden keine Test-Mails versendet. Telefon und Mobil bewusst leer gelassen.</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>GELB   "Allgemeiner offizieller Kontakt" = Funktionsadresse, weil kein persoenliches Postfach veroeffentlicht ist. Anschreiben mit Weiterleitungsbitte.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Adresse = Sitz der adressierten Gesellschaft. Abweichende Arbeitsorte: Dr. Regierer sitzt in Berlin (Alt-Moabit 2, 10557 Berlin), S. Schaible in Frankfurt (OpernTurm, Bockenheimer Landstr. 2-8, 60306 Frankfurt).</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>ROT    "SCHWACH BELEGT" = Domain gesichert, Personenschema nicht. Vor Versand pruefen.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher bewusst auf UK-Ebene (FRP: keine deutsche Gesellschaft; Piper Sandler Muenchen = Research/Equity-Distribution).</t>
-        </is>
-      </c>
+      <c r="A18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Stifel: DACH-Advisory-Fuehrung im Wechsel (J. Lucas ausgeschieden 11/2024; T. Klack seit 12/2025 nicht mehr Geschaeftsfuehrer). Rolle vor Versand verifizieren.</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Weitere Hinweise</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Alvarez &amp; Marsal: zweiter gleichrangiger Co-Head ist Patrick Siebert; bestaetigte Direktadresse liegt fuer Johann Stohner (Head of Restructuring Germany) vor: jstohner@alvarezandmarsal.com.</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Adresse = Sitz der adressierten Gesellschaft bzw. des adressierten Bueros. Abweichende Arbeitsorte: Dr. Regierer sitzt in Berlin (Alt-Moabit 2, 10557 Berlin), S. Schaible in Frankfurt (OpernTurm, Bockenheimer Landstr. 2-8, 60306 Frankfurt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Alvarez &amp; Marsal: Kontakt bewusst Johann Stohner, weil dessen Adresse veroeffentlicht ist. Die beiden Co-Heads Deutschland sind Juergen Zapf und Patrick Siebert; fuer sie ist nur der allgemeine Kanal infode@alvarezandmarsal.com gesichert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Stifel: DACH-Advisory-Fuehrung im Wechsel (J. Lucas ausgeschieden 11/2024, T. Klack seit 12/2025 nicht mehr Geschaeftsfuehrer). Stippler ist als MD Frankfurt und eingetragener Geschaeftsfuehrer belegt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher auf UK-Ebene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Telefonnummern sind Zentralen, sofern nicht als Durchwahl/Mobil ausgewiesen. Es wurden keine Test-Mails versendet.</t>
         </is>
       </c>
     </row>

--- a/Contact_Log_Consulting_Partner_DACH.xlsx
+++ b/Contact_Log_Consulting_Partner_DACH.xlsx
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,7 +72,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -555,32 +555,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Johann Stohner</t>
+          <t>Jürgen Zapf</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Head of Restructuring Germany</t>
+          <t>Managing Director, Co-Head A&amp;M Deutschland (Führungstrio mit Patrick Siebert und Bob Rajan); Head of German Transaction Advisory Group</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+49 89 71040 600</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>+49 170 921 3836</t>
-        </is>
-      </c>
+          <t>+49 89 710 40 600</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>jstohner@alvarezandmarsal.com</t>
+          <t>jzapf@alvarezandmarsal.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>BESTÄTIGT - https://www.germany-alvarezandmarsal.com/en/contact-us (Adresse dort mit Telefonnummer veröffentlicht)</t>
+          <t>WIDERSPRUCH - Firmenschema [Initial][Nachname] ohne Punkt, belegt durch jstohner@alvarezandmarsal.com auf der offiziellen Kontaktseite. Finance ThinkTank (Dritte) listet ihn dagegen als j.zapf@alvarezandmarsal.com MIT Punkt. Nicht aufgelöst - Rückfall: infode@alvarezandmarsal.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -659,12 +655,12 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>geoff.rowley@frpadvisory.com</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>BESTÄTIGT - https://www.frpadvisory.com/about-us/our-people/geoff-rowley/</t>
         </is>
@@ -702,14 +698,14 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>contact-de@capitalmind.com</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Allgemeiner offizieller Kontakt - https://capitalmind.com/contact/ (persönliches Postfach nicht veröffentlicht; Domainwechsel Richtung investec.com laufend)</t>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - https://capitalmind.com/contact/. WARNUNG: juergen.schwarz@investec.com ist NICHT belegt. Drei Domains konkurrieren: capitalmind.com (Advisory-Einheit, offiziell), investec.com (Teamseiten) und investecmail.com (Investec Frankfurt, historisch).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -741,12 +737,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>christian.hess@psc.com</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>SCHWACH BELEGT - Maildomain psc.com offiziell (investorrelations@psc.com), Personenschema vorname.nachname aber nur über maskierte Datenbank-Treffer. Vor Versand verifizieren.</t>
         </is>
@@ -775,7 +771,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Business Services / Diversified Industries Investment Banking, Frankfurt</t>
+          <t>Managing Director, Business Services / Diversified Industries Investment Banking Group, Frankfurt; laut Handelsregister Geschäftsführer Stifel Europe Advisory GmbH</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -784,12 +780,12 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>christian.stippler@stifel.com</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>BESTÄTIGT - https://stifelinstitutional.com/meet/christian-stippler/ (Adresse, Telefon und v-Card auf der Profilseite)</t>
         </is>
@@ -827,14 +823,14 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>contact-de@forvismazars.com</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Allgemeiner offizieller Kontakt - https://www.forvismazars.com/de/de/legals/impressum (persönliches Postfach nicht veröffentlicht; Altdomain mazars.de parallel aktiv)</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - https://www.forvismazars.com/de/de/legals/impressum. WARNUNG: christoph.regierer@forvismazars.com ist nur ueber Hunter.io belegt - nach SOP Abschnitt 6 kein zulaessiger Alleinbeleg. Altdomain mazars.de parallel aktiv.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1004,7 +1000,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>ROT    "SCHWACH BELEGT" = Domain gesichert, Personenschema nicht. Vor Versand pruefen.</t>
+          <t>ROT    "SCHWACH BELEGT" / "WIDERSPRUCH" / "WARNUNG" = Beleglage unzureichend oder Quellen widersprechen sich. Vor Versand zwingend pruefen.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1024,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal: Kontakt bewusst Johann Stohner, weil dessen Adresse veroeffentlicht ist. Die beiden Co-Heads Deutschland sind Juergen Zapf und Patrick Siebert; fuer sie ist nur der allgemeine Kanal infode@alvarezandmarsal.com gesichert.</t>
+          <t>Alvarez &amp; Marsal: A&amp;M Deutschland wird von einem Trio gefuehrt - Juergen Zapf, Patrick Siebert, Bob Rajan. Deutsche Zentrale ist Muenchen, nicht Frankfurt. Einzige bestaetigte Direktadresse im deutschen Team: jstohner@alvarezandmarsal.com (Johann Stohner, Head of Restructuring Germany, Muenchen, Mobil +49 170 921 3836) - als Alternative mit gesicherter Adresse.</t>
         </is>
       </c>
     </row>

--- a/Contact_Log_Consulting_Partner_DACH.xlsx
+++ b/Contact_Log_Consulting_Partner_DACH.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Contact Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact Log'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact Log'!$A$1:$L$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -102,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -113,14 +119,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -498,6 +507,9 @@
     <col width="62" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -546,6 +558,21 @@
           <t>Adresse</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -589,6 +616,21 @@
           <t>Alvarez &amp; Marsal Deutschland GmbH, Sonnenstraße 20, 80331 München</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.germany-alvarezandmarsal.com</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="50" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -612,12 +654,12 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>christian.saeuberlich@fti-andersch.com</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Firmenschema (zwei Belege: leoni.juschkat@ und ellina.hanxleden@fti-andersch.com; Umlaut-Schreibweise gestützt durch Seiten-URL .../management/christian-saeuberlich/) - Rückfall: info@fti-andersch.com</t>
         </is>
@@ -630,6 +672,21 @@
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>FTI-Andersch AG, Taunusanlage 9-10, 60329 Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fti-andersch.com</t>
         </is>
       </c>
     </row>
@@ -655,12 +712,12 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>geoff.rowley@frpadvisory.com</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>BESTÄTIGT - https://www.frpadvisory.com/about-us/our-people/geoff-rowley/</t>
         </is>
@@ -673,6 +730,21 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>FRP Advisory Group plc, 110 Cannon Street, London EC4N 6EU, United Kingdom</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Vereinigtes Königreich</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.frpadvisory.com</t>
         </is>
       </c>
     </row>
@@ -716,6 +788,21 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Investec Advisory GmbH &amp; Co. KG, Sonnenberger Straße 16, 65193 Wiesbaden</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>https://capitalmind.com</t>
         </is>
       </c>
     </row>
@@ -757,6 +844,21 @@
           <t>Piper Sandler Ltd., 2 Gresham Street, 6th Floor, London, United Kingdom</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Vereinigtes Königreich</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pipersandler.com</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -780,12 +882,12 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>christian.stippler@stifel.com</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>BESTÄTIGT - https://stifelinstitutional.com/meet/christian-stippler/ (Adresse, Telefon und v-Card auf der Profilseite)</t>
         </is>
@@ -798,6 +900,21 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Stifel Europe Advisory GmbH, Luginsland 1, 60313 Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.stifel.com</t>
         </is>
       </c>
     </row>
@@ -843,6 +960,21 @@
           <t>Forvis Mazars GmbH &amp; Co. KG, Domstraße 15, 20095 Hamburg</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.forvismazars.com/de/de</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -866,12 +998,12 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>fabian.brandt@oliverwyman.com</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Firmenschema (drei Belege auf oliverwyman.de: felix.wilker@, davina.lermer-spitzweg@, aleksandar.nikolov@oliverwyman.com)</t>
         </is>
@@ -884,6 +1016,21 @@
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Oliver Wyman GmbH, Müllerstraße 3, 80469 München</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oliverwyman.de</t>
         </is>
       </c>
     </row>
@@ -909,12 +1056,12 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>stefan.schaible@rolandberger.com</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Firmenschema (drei Belege im offiziellen Newsroom: silvia.zoesch@, julia.frank@, philipp.topitsch@rolandberger.com)</t>
         </is>
@@ -927,6 +1074,21 @@
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Roland Berger GmbH, Sederanger 1, 80538 München</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rolandberger.com</t>
         </is>
       </c>
     </row>
@@ -948,12 +1110,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>jens.nawrath@ankura.com</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Firmenschema, nur EIN Beleg (robin.boesen@ankura.com aus der offiziellen Pressemitteilung vom 14.08.2025) - vor Versand verifizieren</t>
         </is>
@@ -968,89 +1130,116 @@
           <t>Ankura Consulting Group, Taunusanlage 21, 60325 Frankfurt am Main</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>https://ankura.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Legende Spalte "Herkunft Email" (Farbe in Spalte Email/Herkunft)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>GRUEN  "BESTAETIGT" + URL = Adresse steht so auf der genannten offiziellen Unternehmensseite. Direkt verwendbar.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>GELB   "Firmenschema" = aus dem belegten Muster desselben Unternehmens gebildet, Mailbox nicht verifiziert. Anzahl der Belege ist jeweils genannt.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>GELB   "Allgemeiner offizieller Kontakt" = Funktionsadresse, weil kein persoenliches Postfach veroeffentlicht ist. Anschreiben mit Weiterleitungsbitte.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ROT    "SCHWACH BELEGT" / "WIDERSPRUCH" / "WARNUNG" = Beleglage unzureichend oder Quellen widersprechen sich. Vor Versand zwingend pruefen.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Weitere Hinweise</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Adresse = Sitz der adressierten Gesellschaft bzw. des adressierten Bueros. Abweichende Arbeitsorte: Dr. Regierer sitzt in Berlin (Alt-Moabit 2, 10557 Berlin), S. Schaible in Frankfurt (OpernTurm, Bockenheimer Landstr. 2-8, 60306 Frankfurt).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Alvarez &amp; Marsal: A&amp;M Deutschland wird von einem Trio gefuehrt - Juergen Zapf, Patrick Siebert, Bob Rajan. Deutsche Zentrale ist Muenchen, nicht Frankfurt. Einzige bestaetigte Direktadresse im deutschen Team: jstohner@alvarezandmarsal.com (Johann Stohner, Head of Restructuring Germany, Muenchen, Mobil +49 170 921 3836) - als Alternative mit gesicherter Adresse.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Stifel: DACH-Advisory-Fuehrung im Wechsel (J. Lucas ausgeschieden 11/2024, T. Klack seit 12/2025 nicht mehr Geschaeftsfuehrer). Stippler ist als MD Frankfurt und eingetragener Geschaeftsfuehrer belegt.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher auf UK-Ebene.</t>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher auf UK-Ebene. Land und Region beziehen sich immer auf die adressierte Gesellschaft, nicht auf den Konzernsitz: Piper Sandler (Minneapolis), Stifel (St. Louis), Alvarez &amp; Marsal (New York) und Ankura (Washington D.C.) sind US-Haeuser, angesprochen wird aber jeweils die europaeische Einheit.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Telefonnummern sind Zentralen, sofern nicht als Durchwahl/Mobil ausgewiesen. Es wurden keine Test-Mails versendet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:L11"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Contact_Log_Consulting_Partner_DACH.xlsx
+++ b/Contact_Log_Consulting_Partner_DACH.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Contact Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact Log'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact Log'!$A$1:$L$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1146,88 +1146,611 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Cedra</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Pontus Tonning</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, Cedra Group (zuvor Assurance Leader PwC Schweden)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>+46 10 212 40 00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>+46 709 29 12 12</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>pontus.tonning@cedra.se</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Veroeffentlicht laut Suchtreffer (Cedra-Kontaktangabe mit Telefonnummer) - Seite nicht geoeffnet, Egress gesperrt</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Cedra Sverige AB, Torsgatan 21, 113 97 Stockholm, Schweden</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Schweden</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>https://cedragroup.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Cherry Bekaert</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michelle Loyd Thompson</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, Cherry Bekaert Advisory LLC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>michelle.thompson@cbh.com</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>SCHWACH BELEGT - Format First.Last@cbh.com nur ueber Aggregator; Zweitname "Loyd" macht die Adressform unsicher. Offizieller Weg: cbh.com/contact/find-a-press-contact/</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Frau</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Cherry Bekaert, 3800 Glenwood Ave, Raleigh, NC 27612, USA</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Amerika</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cbh.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DJH (Mitten Clarke)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Scott Heath</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, DJH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>+44 1782 279615</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>info@djh.co.uk</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - djh.co.uk/offices/stoke-on-trent/. Persoenliches Schema unbelegt, belegt sind nur Standortadressen (z. B. bexley@djh.co.uk)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>DJH, The Glades, Festival Way, Festival Park, Stoke-on-Trent, Staffordshire ST1 5SQ, UK</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Vereinigtes Königreich</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.djh.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Grant Thornton</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Heike Wieland-Blöse</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Sprecherin des Vorstands / CEO Grant Thornton Deutschland</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>+49 211 9524 0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>heike.wieland-bloese@de.gt.com</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Firmenschema (zwei Belege: willi.keipper@de.gt.com und mandy.zingsem@de.gt.com). WARNUNG: Umlaut in "Bloese" nicht belegt. Rueckfall: request@de.gt.com</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Frau</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Grant Thornton AG Wirtschaftsprüfungsgesellschaft, Johannstraße 39, 40476 Düsseldorf</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.grantthornton.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Kroll</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Fluhrer</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Co-Head of Restructuring Europe</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 388884016</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Andreas.Fluhrer@kroll.com</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Firmenschema, ein Beleg (Emma.Thompson@kroll.com aus offizieller Kroll-Pressemitteilung). Sammelkanal: mediarelations@kroll.com</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Kroll, Büro München - Strassenanschrift nicht belegt (kroll.com/en/global-locations/europe-and-middle-east/munich)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kroll.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Julia Arbery</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Partner DACH, StoneTurn - a Province company</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>+49 69 710 455 457</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>julia.arbery@stoneturn.com</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>SCHWACH BELEGT - kein Beleg fuer ein Personenschema auf stoneturn.com; belegt ist nur press@stoneturn.com. Vor Versand pruefen.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Frau</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>StoneTurn Group (Germany) GmbH, Bockenheimer Landstraße 17/19, 60325 Frankfurt am Main (Registeranschrift abweichend: Bockenheimer Landstraße 2-4, 60306)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>https://provincefirm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Teneo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Marcel Herter</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Managing Director Teneo; Gründer und Leiter von Herter &amp; Co., Teneos Financial-Advisory-Geschäft in Deutschland</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>+49 69 867 906 056</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>marcel.herter@teneo.com</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>SCHWACH BELEGT - kein Formatbeleg fuer teneo.com gefunden; zweite moegliche Domain herter-co.de. Vor Versand pruefen.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Teneo Germany GmbH, Neue Mainzer Straße 80, 60311 Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.teneo.com/germany/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WTS Global</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Fritz Esterer</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Group CEO WTS Global (verantwortet ausdrücklich Akquisitionen und den Aufbau neuer Ländergesellschaften); Vorstand WTS Group AG</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 28646-0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>info@wts.de</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Allgemeiner offizieller Kontakt - wts.com/de-de/impressum. Persoenliches Schema unbelegt.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WTS Group AG, Thomas-Wimmer-Ring 1, 80539 München (Registeranschrift; Quellen nennen auch Nr. 3. Operative Gesellschaften: Friedenstraße 22, 81671 München)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>https://wts.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Legende Spalte "Herkunft Email" (Farbe in Spalte Email/Herkunft)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>GRUEN  "BESTAETIGT" + URL = Adresse steht so auf der genannten offiziellen Unternehmensseite. Direkt verwendbar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>GELB   "Firmenschema" = aus dem belegten Muster desselben Unternehmens gebildet, Mailbox nicht verifiziert. Anzahl der Belege ist jeweils genannt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>GELB   "Allgemeiner offizieller Kontakt" = Funktionsadresse, weil kein persoenliches Postfach veroeffentlicht ist. Anschreiben mit Weiterleitungsbitte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>ROT    "SCHWACH BELEGT" / "WIDERSPRUCH" / "WARNUNG" = Beleglage unzureichend oder Quellen widersprechen sich. Vor Versand zwingend pruefen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Weitere Hinweise</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Adresse = Sitz der adressierten Gesellschaft bzw. des adressierten Bueros. Abweichende Arbeitsorte: Dr. Regierer sitzt in Berlin (Alt-Moabit 2, 10557 Berlin), S. Schaible in Frankfurt (OpernTurm, Bockenheimer Landstr. 2-8, 60306 Frankfurt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Alvarez &amp; Marsal: A&amp;M Deutschland wird von einem Trio gefuehrt - Juergen Zapf, Patrick Siebert, Bob Rajan. Deutsche Zentrale ist Muenchen, nicht Frankfurt. Einzige bestaetigte Direktadresse im deutschen Team: jstohner@alvarezandmarsal.com (Johann Stohner, Head of Restructuring Germany, Muenchen, Mobil +49 170 921 3836) - als Alternative mit gesicherter Adresse.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Stifel: DACH-Advisory-Fuehrung im Wechsel (J. Lucas ausgeschieden 11/2024, T. Klack seit 12/2025 nicht mehr Geschaeftsfuehrer). Stippler ist als MD Frankfurt und eingetragener Geschaeftsfuehrer belegt.</t>
+          <t>GRUEN  "BESTAETIGT" + URL = Adresse steht so auf der genannten offiziellen Unternehmensseite. Direkt verwendbar.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher auf UK-Ebene. Land und Region beziehen sich immer auf die adressierte Gesellschaft, nicht auf den Konzernsitz: Piper Sandler (Minneapolis), Stifel (St. Louis), Alvarez &amp; Marsal (New York) und Ankura (Washington D.C.) sind US-Haeuser, angesprochen wird aber jeweils die europaeische Einheit.</t>
+          <t>GELB   "Firmenschema" = aus dem belegten Muster desselben Unternehmens gebildet, Mailbox nicht verifiziert. Anzahl der Belege ist jeweils genannt.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>GELB   "Allgemeiner offizieller Kontakt" = Funktionsadresse, weil kein persoenliches Postfach veroeffentlicht ist. Anschreiben mit Weiterleitungsbitte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>ROT    "SCHWACH BELEGT" / "WIDERSPRUCH" / "WARNUNG" = Beleglage unzureichend oder Quellen widersprechen sich. Vor Versand zwingend pruefen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Weitere Hinweise</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Adresse = Sitz der adressierten Gesellschaft bzw. des adressierten Bueros. Abweichende Arbeitsorte: Dr. Regierer sitzt in Berlin (Alt-Moabit 2, 10557 Berlin), S. Schaible in Frankfurt (OpernTurm, Bockenheimer Landstr. 2-8, 60306 Frankfurt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Alvarez &amp; Marsal: A&amp;M Deutschland wird von einem Trio gefuehrt - Juergen Zapf, Patrick Siebert, Bob Rajan. Deutsche Zentrale ist Muenchen, nicht Frankfurt. Einzige bestaetigte Direktadresse im deutschen Team: jstohner@alvarezandmarsal.com (Johann Stohner, Head of Restructuring Germany, Muenchen, Mobil +49 170 921 3836) - als Alternative mit gesicherter Adresse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Stifel: DACH-Advisory-Fuehrung im Wechsel (J. Lucas ausgeschieden 11/2024, T. Klack seit 12/2025 nicht mehr Geschaeftsfuehrer). Stippler ist als MD Frankfurt und eingetragener Geschaeftsfuehrer belegt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>FRP und Piper Sandler haben keine deutsche Partnerebene - Kontakt daher auf UK-Ebene. Land und Region beziehen sich immer auf die adressierte Gesellschaft, nicht auf den Konzernsitz: Piper Sandler (Minneapolis), Stifel (St. Louis), Alvarez &amp; Marsal (New York) und Ankura (Washington D.C.) sind US-Haeuser, angesprochen wird aber jeweils die europaeische Einheit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t>Telefonnummern sind Zentralen, sofern nicht als Durchwahl/Mobil ausgewiesen. Es wurden keine Test-Mails versendet.</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Zur zweiten Tranche (Zeilen 11-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Cedra: nordischer Konsolidierer, 2025 aus fuenf schwedischen Pruefungsgesellschaften plus Adelis Equity entstanden, Carve-outs von PwC Schweden und Deloitte Norwegen. Kein deutsches Buero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Cherry Bekaert: reine US-Firma, kein europaeisches Buero. Region daher Amerika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>DJH: firmiert seit April 2024 nur noch als DJH, PE-gestuetzt (Tenzing), rund 900 Mitarbeiter an 19 Standorten in UK und Irland. Fuer eine Akquisitionsansprache oft besser: Richard Crook, Mergers and Acquisitions Director.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Kroll: Andreas Stoecklin, bis dahin Country Leader Germany und Head of EMEA Corporate Finance, ist zu FTI Consulting/FTI-Andersch gewechselt. Kroll Deutschland hat in den Quellen keinen ausgewiesenen Country Head mehr; Fluhrer ist der ranghoechste deutsche Restrukturierungspartner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Province: erst durch die Uebernahme von StoneTurn im Februar 2026 in Deutschland praesent. Ueber Zukaeufe entscheidet Province in den USA (Peter Kravitz, Paul Huygens; Trivest Partners als Investor). Kristof Wabl, frueher StoneTurn DACH, ist inzwischen bei AlixPartners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Teneo: hat Herter &amp; Co. im September 2023 uebernommen, Herter fuehrt das Geschaeft weiter (Frankfurt und Berlin). Die eingetragenen Geschaeftsfuehrer der Teneo Germany GmbH (Philippe Blanchard, Susan Couldery) sind Konzernfunktionen, keine deutschen Marktpartner. Weiterer deutscher SMD bei Herter &amp; Co.: Michael Spahn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>WTS: Fuehrungswechsel Mitte 2026 - Bjoern Viebrock (zuvor PwC-Vorstand) wurde CEO WTS Deutschland und Group COO. Esterer, seit 2009 Vorstandsvorsitzender, fuehrt als Group CEO die internationale Holding weiter, ausdruecklich zustaendig fuer Akquisitionen - deshalb hier gesetzt. Fuer rein deutsche Themen ist Viebrock der Ansprechpartner.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1239,6 +1762,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
